--- a/salidas/empresas/SO.xlsx
+++ b/salidas/empresas/SO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.9489860534668</v>
+        <v>13.94898891448975</v>
       </c>
       <c r="C2" t="n">
         <v>34.79999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78856372833252</v>
+        <v>13.78856468200684</v>
       </c>
       <c r="C3" t="n">
         <v>34.02999877929688</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.27802467346191</v>
+        <v>13.2780237197876</v>
       </c>
       <c r="C4" t="n">
         <v>32.77000045776367</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.2213020324707</v>
+        <v>13.22130489349365</v>
       </c>
       <c r="C5" t="n">
         <v>32.22999954223633</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.11464881896973</v>
+        <v>13.11464691162109</v>
       </c>
       <c r="C6" t="n">
         <v>31.96999931335449</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1474666595459</v>
+        <v>13.14746570587158</v>
       </c>
       <c r="C7" t="n">
         <v>32.04999923706055</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85715007781982</v>
+        <v>13.85714626312256</v>
       </c>
       <c r="C8" t="n">
         <v>33.77999877929688</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.21947193145752</v>
+        <v>14.21947574615479</v>
       </c>
       <c r="C9" t="n">
         <v>34.27000045776367</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.1032600402832</v>
+        <v>15.10326480865479</v>
       </c>
       <c r="C11" t="n">
         <v>36.40000152587891</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>15.20213222503662</v>
+        <v>15.20213413238525</v>
       </c>
       <c r="C12" t="n">
         <v>36.25</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>15.45795631408691</v>
+        <v>15.45794582366943</v>
       </c>
       <c r="C13" t="n">
         <v>36.86000061035156</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>15.31955528259277</v>
+        <v>15.31956100463867</v>
       </c>
       <c r="C14" t="n">
         <v>36.52999877929688</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>15.17459297180176</v>
+        <v>15.17459774017334</v>
       </c>
       <c r="C15" t="n">
         <v>35.79999923706055</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>15.53488540649414</v>
+        <v>15.53488063812256</v>
       </c>
       <c r="C16" t="n">
         <v>36.65000152587891</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>16.01810073852539</v>
+        <v>16.01809883117676</v>
       </c>
       <c r="C17" t="n">
         <v>37.79000091552734</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.42694854736328</v>
+        <v>15.42695426940918</v>
       </c>
       <c r="C18" t="n">
         <v>36.0099983215332</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.41162395477295</v>
+        <v>14.41163063049316</v>
       </c>
       <c r="C20" t="n">
         <v>33.63999938964844</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.38175201416016</v>
+        <v>15.38175296783447</v>
       </c>
       <c r="C21" t="n">
         <v>35.4900016784668</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.72414779663086</v>
+        <v>15.72414016723633</v>
       </c>
       <c r="C22" t="n">
         <v>36.27999877929688</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.88883876800537</v>
+        <v>15.88884162902832</v>
       </c>
       <c r="C23" t="n">
         <v>36.65999984741211</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.98134231567383</v>
+        <v>16.98133659362793</v>
       </c>
       <c r="C25" t="n">
         <v>38.75</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>16.11684989929199</v>
+        <v>16.11684799194336</v>
       </c>
       <c r="C26" t="n">
         <v>36.36999893188477</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>15.30147743225098</v>
+        <v>15.30147933959961</v>
       </c>
       <c r="C27" t="n">
         <v>34.52999877929688</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.78006744384766</v>
+        <v>15.78006553649902</v>
       </c>
       <c r="C28" t="n">
         <v>35.61000061035156</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.49794578552246</v>
+        <v>16.49794769287109</v>
       </c>
       <c r="C29" t="n">
         <v>37.22999954223633</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.22454452514648</v>
+        <v>16.22455596923828</v>
       </c>
       <c r="C30" t="n">
         <v>36.20000076293945</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.6508617401123</v>
+        <v>15.65085887908936</v>
       </c>
       <c r="C31" t="n">
         <v>34.91999816894531</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>16.0494327545166</v>
+        <v>16.04943466186523</v>
       </c>
       <c r="C32" t="n">
         <v>35.38999938964844</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.01086235046387</v>
+        <v>17.0108585357666</v>
       </c>
       <c r="C33" t="n">
         <v>37.5099983215332</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.09248924255371</v>
+        <v>17.09248733520508</v>
       </c>
       <c r="C34" t="n">
         <v>37.68999862670898</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.76356983184814</v>
+        <v>15.76355934143066</v>
       </c>
       <c r="C35" t="n">
         <v>34.34000015258789</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>16.6724681854248</v>
+        <v>16.67246627807617</v>
       </c>
       <c r="C36" t="n">
         <v>36.31999969482422</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.54497528076172</v>
+        <v>15.54497337341309</v>
       </c>
       <c r="C38" t="n">
         <v>33.45000076293945</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.08574962615967</v>
+        <v>14.08573818206787</v>
       </c>
       <c r="C39" t="n">
         <v>30.30999946594238</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.61983585357666</v>
+        <v>13.61984252929688</v>
       </c>
       <c r="C41" t="n">
         <v>28.8799991607666</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.69509124755859</v>
+        <v>14.69508934020996</v>
       </c>
       <c r="C43" t="n">
         <v>31.15999984741211</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>15.01502323150635</v>
+        <v>15.01501655578613</v>
       </c>
       <c r="C44" t="n">
         <v>31.39999961853027</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>14.91939163208008</v>
+        <v>14.91937828063965</v>
       </c>
       <c r="C45" t="n">
         <v>31.20000076293945</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.14413070678711</v>
+        <v>15.14412975311279</v>
       </c>
       <c r="C46" t="n">
         <v>31.67000007629395</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.11815929412842</v>
+        <v>15.1181583404541</v>
       </c>
       <c r="C47" t="n">
         <v>31.19000053405762</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.55440711975098</v>
+        <v>15.55440330505371</v>
       </c>
       <c r="C48" t="n">
         <v>32.09000015258789</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>16.15059471130371</v>
+        <v>16.15059280395508</v>
       </c>
       <c r="C49" t="n">
         <v>33.31999969482422</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.71999645233154</v>
+        <v>15.71999359130859</v>
       </c>
       <c r="C50" t="n">
         <v>32</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.607008934021</v>
+        <v>15.60700416564941</v>
       </c>
       <c r="C51" t="n">
         <v>31.77000045776367</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.28984260559082</v>
+        <v>16.28984069824219</v>
       </c>
       <c r="C52" t="n">
         <v>33.15999984741211</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.19954490661621</v>
+        <v>17.19954299926758</v>
       </c>
       <c r="C53" t="n">
         <v>34.56000137329102</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.27387237548828</v>
+        <v>16.27387046813965</v>
       </c>
       <c r="C54" t="n">
         <v>32.70000076293945</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.56251907348633</v>
+        <v>16.5625171661377</v>
       </c>
       <c r="C55" t="n">
         <v>33.27999877929688</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.80414581298828</v>
+        <v>17.80413627624512</v>
       </c>
       <c r="C56" t="n">
         <v>35.33000183105469</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>18.48949813842773</v>
+        <v>18.48950004577637</v>
       </c>
       <c r="C57" t="n">
         <v>36.68999862670898</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.76666831970215</v>
+        <v>18.76667213439941</v>
       </c>
       <c r="C58" t="n">
         <v>37.2400016784668</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>19.31359672546387</v>
+        <v>19.31358909606934</v>
       </c>
       <c r="C59" t="n">
         <v>37.86999893188477</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.23709869384766</v>
+        <v>19.23709106445312</v>
       </c>
       <c r="C60" t="n">
         <v>37.72000122070312</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.49719047546387</v>
+        <v>19.49718856811523</v>
       </c>
       <c r="C61" t="n">
         <v>38.22999954223633</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.18609046936035</v>
+        <v>19.18608665466309</v>
       </c>
       <c r="C62" t="n">
         <v>37.61999893188477</v>
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>20.40205383300781</v>
+        <v>20.40205764770508</v>
       </c>
       <c r="C65" t="n">
         <v>39.04000091552734</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>20.945556640625</v>
+        <v>20.94554901123047</v>
       </c>
       <c r="C66" t="n">
         <v>40.08000183105469</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.10233116149902</v>
+        <v>21.10232543945312</v>
       </c>
       <c r="C67" t="n">
         <v>40.38000106811523</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>20.90937423706055</v>
+        <v>20.90937232971191</v>
       </c>
       <c r="C68" t="n">
         <v>39.54000091552734</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>21.87182235717773</v>
+        <v>21.87182998657227</v>
       </c>
       <c r="C69" t="n">
         <v>41.36000061035156</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.40592193603516</v>
+        <v>22.40592384338379</v>
       </c>
       <c r="C70" t="n">
         <v>42.36999893188477</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.8448486328125</v>
+        <v>22.8448371887207</v>
       </c>
       <c r="C71" t="n">
         <v>43.20000076293945</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>23.47717475891113</v>
+        <v>23.47718048095703</v>
       </c>
       <c r="C72" t="n">
         <v>43.90999984741211</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>24.74968719482422</v>
+        <v>24.74967575073242</v>
       </c>
       <c r="C73" t="n">
         <v>46.29000091552734</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>24.359375</v>
+        <v>24.3593692779541</v>
       </c>
       <c r="C74" t="n">
         <v>45.56000137329102</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>23.87573623657227</v>
+        <v>23.8757438659668</v>
       </c>
       <c r="C75" t="n">
         <v>44.18999862670898</v>
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.82126426696777</v>
+        <v>24.82126235961914</v>
       </c>
       <c r="C77" t="n">
         <v>45.93999862670898</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>25.07271575927734</v>
+        <v>25.07271003723145</v>
       </c>
       <c r="C78" t="n">
         <v>45.90999984741211</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.28570365905762</v>
+        <v>25.28569984436035</v>
       </c>
       <c r="C79" t="n">
         <v>46.29999923706055</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.29604530334473</v>
+        <v>26.29604339599609</v>
       </c>
       <c r="C80" t="n">
         <v>48.15000152587891</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.01187515258789</v>
+        <v>25.01187896728516</v>
       </c>
       <c r="C81" t="n">
         <v>45.33000183105469</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.43122673034668</v>
+        <v>25.43121528625488</v>
       </c>
       <c r="C82" t="n">
         <v>46.09000015258789</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.84505271911621</v>
+        <v>25.84505844116211</v>
       </c>
       <c r="C83" t="n">
         <v>46.84000015258789</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.28375053405762</v>
+        <v>24.28376007080078</v>
       </c>
       <c r="C84" t="n">
         <v>43.54999923706055</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>23.87113380432129</v>
+        <v>23.87112998962402</v>
       </c>
       <c r="C85" t="n">
         <v>42.81000137329102</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.93734169006348</v>
+        <v>24.93733406066895</v>
       </c>
       <c r="C86" t="n">
         <v>44.22999954223633</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.37710571289062</v>
+        <v>25.37709999084473</v>
       </c>
       <c r="C87" t="n">
         <v>45.0099983215332</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.4539852142334</v>
+        <v>26.45397758483887</v>
       </c>
       <c r="C88" t="n">
         <v>46.91999816894531</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>27.19256973266602</v>
+        <v>27.19257354736328</v>
       </c>
       <c r="C89" t="n">
         <v>48.22999954223633</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.01640129089355</v>
+        <v>25.01639366149902</v>
       </c>
       <c r="C90" t="n">
         <v>43.90000152587891</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.1474609375</v>
+        <v>25.14746856689453</v>
       </c>
       <c r="C91" t="n">
         <v>44.13000106811523</v>
@@ -2590,7 +2602,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.98836898803711</v>
+        <v>23.98837089538574</v>
       </c>
       <c r="C93" t="n">
         <v>41.61999893188477</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>23.73477363586426</v>
+        <v>23.73476600646973</v>
       </c>
       <c r="C94" t="n">
         <v>41.18000030517578</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>23.86795616149902</v>
+        <v>23.86796379089355</v>
       </c>
       <c r="C95" t="n">
         <v>40.90999984741211</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>23.70459938049316</v>
+        <v>23.70460319519043</v>
       </c>
       <c r="C96" t="n">
         <v>40.63000106811523</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>23.98463821411133</v>
+        <v>23.98464393615723</v>
       </c>
       <c r="C97" t="n">
         <v>41.11000061035156</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>24.3625659942627</v>
+        <v>24.36257171630859</v>
       </c>
       <c r="C98" t="n">
         <v>41.2400016784668</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>25.01829147338867</v>
+        <v>25.0182991027832</v>
       </c>
       <c r="C99" t="n">
         <v>42.34999847412109</v>
@@ -2822,7 +2834,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>27.07411766052246</v>
+        <v>27.07411193847656</v>
       </c>
       <c r="C101" t="n">
         <v>45.83000183105469</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>26.16277885437012</v>
+        <v>26.16278076171875</v>
       </c>
       <c r="C102" t="n">
         <v>43.77999877929688</v>
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>26.17965507507324</v>
+        <v>26.17965316772461</v>
       </c>
       <c r="C104" t="n">
         <v>43.29000091552734</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>26.85093116760254</v>
+        <v>26.85092735290527</v>
       </c>
       <c r="C105" t="n">
         <v>44.40000152587891</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>26.39736557006836</v>
+        <v>26.39735984802246</v>
       </c>
       <c r="C106" t="n">
         <v>43.65000152587891</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.35694885253906</v>
+        <v>28.35693740844727</v>
       </c>
       <c r="C107" t="n">
         <v>46.36000061035156</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.01143074035645</v>
+        <v>29.01144218444824</v>
       </c>
       <c r="C108" t="n">
         <v>47.43000030517578</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.03904151916504</v>
+        <v>30.03903770446777</v>
       </c>
       <c r="C109" t="n">
         <v>49.11000061035156</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.02381706237793</v>
+        <v>31.02382469177246</v>
       </c>
       <c r="C110" t="n">
         <v>50.72000122070312</v>
@@ -3133,11 +3145,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>28.3183536529541</v>
+        <v>28.31834983825684</v>
       </c>
       <c r="C111" t="n">
         <v>45.79000091552734</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>27.38450622558594</v>
+        <v>27.38449859619141</v>
       </c>
       <c r="C112" t="n">
         <v>44.27999877929688</v>
@@ -3187,7 +3199,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3216,11 +3228,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.36212158203125</v>
+        <v>27.36211395263672</v>
       </c>
       <c r="C114" t="n">
         <v>43.68999862670898</v>
@@ -3245,11 +3257,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>26.24108695983887</v>
+        <v>26.2410831451416</v>
       </c>
       <c r="C115" t="n">
         <v>41.90000152587891</v>
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.01345443725586</v>
+        <v>28.01345634460449</v>
       </c>
       <c r="C116" t="n">
         <v>44.72999954223633</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.50750160217285</v>
+        <v>27.50749778747559</v>
       </c>
       <c r="C117" t="n">
         <v>43.40999984741211</v>
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.3249397277832</v>
+        <v>28.32493782043457</v>
       </c>
       <c r="C118" t="n">
         <v>44.70000076293945</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>28.57839584350586</v>
+        <v>28.57840347290039</v>
       </c>
       <c r="C119" t="n">
         <v>45.09999847412109</v>
@@ -3386,11 +3398,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>28.56804847717285</v>
+        <v>28.56804084777832</v>
       </c>
       <c r="C120" t="n">
         <v>44.54000091552734</v>
@@ -3411,11 +3423,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.01119613647461</v>
+        <v>30.01119041442871</v>
       </c>
       <c r="C121" t="n">
         <v>46.79000091552734</v>
@@ -3436,11 +3448,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.37737083435059</v>
+        <v>31.37737846374512</v>
       </c>
       <c r="C122" t="n">
         <v>48.91999816894531</v>
@@ -3461,11 +3473,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.24754524230957</v>
+        <v>31.24752616882324</v>
       </c>
       <c r="C123" t="n">
         <v>48.18000030517578</v>
@@ -3490,7 +3502,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3519,7 +3531,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3548,11 +3560,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.42558670043945</v>
+        <v>32.42557525634766</v>
       </c>
       <c r="C126" t="n">
         <v>49.43999862670898</v>
@@ -3577,11 +3589,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>35.17361068725586</v>
+        <v>35.17361831665039</v>
       </c>
       <c r="C127" t="n">
         <v>53.63000106811523</v>
@@ -3606,7 +3618,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3635,7 +3647,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3664,11 +3676,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>34.00557708740234</v>
+        <v>34.00559997558594</v>
       </c>
       <c r="C130" t="n">
         <v>51.29999923706055</v>
@@ -3693,7 +3705,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3722,11 +3734,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>31.39896774291992</v>
+        <v>31.39897155761719</v>
       </c>
       <c r="C132" t="n">
         <v>46.81999969482422</v>
@@ -3751,11 +3763,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.98836517333984</v>
+        <v>32.98836898803711</v>
       </c>
       <c r="C133" t="n">
         <v>49.18999862670898</v>
@@ -3780,11 +3792,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>33.14933013916016</v>
+        <v>33.14931488037109</v>
       </c>
       <c r="C134" t="n">
         <v>49.43000030517578</v>
@@ -3809,11 +3821,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.48085784912109</v>
+        <v>34.48085403442383</v>
       </c>
       <c r="C135" t="n">
         <v>50.81999969482422</v>
@@ -3838,7 +3850,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3867,11 +3879,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.7888069152832</v>
+        <v>33.78880310058594</v>
       </c>
       <c r="C137" t="n">
         <v>49.79999923706055</v>
@@ -3896,11 +3908,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>34.74243545532227</v>
+        <v>34.7424430847168</v>
       </c>
       <c r="C138" t="n">
         <v>50.61000061035156</v>
@@ -3925,11 +3937,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>32.86837005615234</v>
+        <v>32.86836242675781</v>
       </c>
       <c r="C139" t="n">
         <v>47.88000106811523</v>
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3983,11 +3995,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>33.52614593505859</v>
+        <v>33.52615356445312</v>
       </c>
       <c r="C141" t="n">
         <v>48.2599983215332</v>
@@ -4012,7 +4024,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>36.26326751708984</v>
+        <v>36.26325988769531</v>
       </c>
       <c r="C143" t="n">
         <v>52.20000076293945</v>
@@ -4070,11 +4082,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>35.97022247314453</v>
+        <v>35.97023391723633</v>
       </c>
       <c r="C144" t="n">
         <v>51.20000076293945</v>
@@ -4099,11 +4111,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>33.78532028198242</v>
+        <v>33.78532409667969</v>
       </c>
       <c r="C145" t="n">
         <v>48.09000015258789</v>
@@ -4128,7 +4140,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4157,11 +4169,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.65048980712891</v>
+        <v>30.65048599243164</v>
       </c>
       <c r="C147" t="n">
         <v>43.06000137329102</v>
@@ -4186,11 +4198,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>31.78937149047852</v>
+        <v>31.78937339782715</v>
       </c>
       <c r="C148" t="n">
         <v>44.65999984741211</v>
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>32.82861328125</v>
+        <v>32.82860946655273</v>
       </c>
       <c r="C149" t="n">
         <v>46.11999893188477</v>
@@ -4244,11 +4256,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>32.40596008300781</v>
+        <v>32.40595626831055</v>
       </c>
       <c r="C150" t="n">
         <v>44.90000152587891</v>
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.42360305786133</v>
+        <v>33.42361068725586</v>
       </c>
       <c r="C151" t="n">
         <v>46.31000137329102</v>
@@ -4302,7 +4314,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4331,11 +4343,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>32.00183486938477</v>
+        <v>32.00184631347656</v>
       </c>
       <c r="C153" t="n">
         <v>43.77999877929688</v>
@@ -4360,11 +4372,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>31.87026977539062</v>
+        <v>31.87027740478516</v>
       </c>
       <c r="C154" t="n">
         <v>43.59999847412109</v>
@@ -4389,7 +4401,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4418,11 +4430,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.04243087768555</v>
+        <v>35.04243850708008</v>
       </c>
       <c r="C156" t="n">
         <v>47.33000183105469</v>
@@ -4447,11 +4459,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>32.51771545410156</v>
+        <v>32.51770782470703</v>
       </c>
       <c r="C157" t="n">
         <v>43.91999816894531</v>
@@ -4476,11 +4488,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>35.98272323608398</v>
+        <v>35.98271179199219</v>
       </c>
       <c r="C158" t="n">
         <v>48.59999847412109</v>
@@ -4505,11 +4517,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>37.24392700195312</v>
+        <v>37.24393844604492</v>
       </c>
       <c r="C159" t="n">
         <v>49.68999862670898</v>
@@ -4534,7 +4546,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4563,7 +4575,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4592,11 +4604,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>40.56485366821289</v>
+        <v>40.56485748291016</v>
       </c>
       <c r="C162" t="n">
         <v>53.5</v>
@@ -4621,11 +4633,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.91449356079102</v>
+        <v>41.91448593139648</v>
       </c>
       <c r="C163" t="n">
         <v>55.27999877929688</v>
@@ -4650,11 +4662,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.612060546875</v>
+        <v>42.6120491027832</v>
       </c>
       <c r="C164" t="n">
         <v>56.20000076293945</v>
@@ -4679,11 +4691,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>44.65439605712891</v>
+        <v>44.65439224243164</v>
       </c>
       <c r="C165" t="n">
         <v>58.2599983215332</v>
@@ -4708,11 +4720,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>47.34469604492188</v>
+        <v>47.34470367431641</v>
       </c>
       <c r="C166" t="n">
         <v>61.77000045776367</v>
@@ -4737,11 +4749,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>48.02685546875</v>
+        <v>48.02685165405273</v>
       </c>
       <c r="C167" t="n">
         <v>62.65999984741211</v>
@@ -4766,7 +4778,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4795,11 +4807,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>49.31403350830078</v>
+        <v>49.31403732299805</v>
       </c>
       <c r="C169" t="n">
         <v>63.70000076293945</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.50090789794922</v>
+        <v>54.50091934204102</v>
       </c>
       <c r="C170" t="n">
         <v>70.40000152587891</v>
@@ -4853,11 +4865,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.14870071411133</v>
+        <v>47.1486930847168</v>
       </c>
       <c r="C171" t="n">
         <v>60.36000061035156</v>
@@ -4882,7 +4894,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4911,7 +4923,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4940,11 +4952,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>45.10607147216797</v>
+        <v>45.1060676574707</v>
       </c>
       <c r="C174" t="n">
         <v>57.06999969482422</v>
@@ -4969,11 +4981,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>40.98037338256836</v>
+        <v>40.98036956787109</v>
       </c>
       <c r="C175" t="n">
         <v>51.84999847412109</v>
@@ -4998,11 +5010,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>43.16176986694336</v>
+        <v>43.16177368164062</v>
       </c>
       <c r="C176" t="n">
         <v>54.61000061035156</v>
@@ -5027,11 +5039,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>41.72664260864258</v>
+        <v>41.72665405273438</v>
       </c>
       <c r="C177" t="n">
         <v>52.18000030517578</v>
@@ -5056,11 +5068,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>43.35797119140625</v>
+        <v>43.35796737670898</v>
       </c>
       <c r="C178" t="n">
         <v>54.22000122070312</v>
@@ -5085,11 +5097,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>45.94089508056641</v>
+        <v>45.94089126586914</v>
       </c>
       <c r="C179" t="n">
         <v>57.45000076293945</v>
@@ -5114,7 +5126,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5143,11 +5155,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>49.62356185913086</v>
+        <v>49.62356567382812</v>
       </c>
       <c r="C181" t="n">
         <v>61.43000030517578</v>
@@ -5172,7 +5184,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5201,7 +5213,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>50.74311828613281</v>
+        <v>50.74312210083008</v>
       </c>
       <c r="C184" t="n">
         <v>62.15999984741211</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>54.01659774780273</v>
+        <v>54.01660919189453</v>
       </c>
       <c r="C185" t="n">
         <v>66.16999816894531</v>
@@ -5288,11 +5300,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>52.70911407470703</v>
+        <v>52.7091178894043</v>
       </c>
       <c r="C186" t="n">
         <v>63.91999816894531</v>
@@ -5317,7 +5329,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5346,7 +5358,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5375,11 +5387,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>54.75151443481445</v>
+        <v>54.75151824951172</v>
       </c>
       <c r="C189" t="n">
         <v>65.73000335693359</v>
@@ -5404,7 +5416,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5433,11 +5445,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>51.91107177734375</v>
+        <v>51.91106796264648</v>
       </c>
       <c r="C191" t="n">
         <v>62.31999969482422</v>
@@ -5462,7 +5474,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5491,11 +5503,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>57.72980117797852</v>
+        <v>57.72979354858398</v>
       </c>
       <c r="C193" t="n">
         <v>68.58000183105469</v>
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.49583053588867</v>
+        <v>58.49583435058594</v>
       </c>
       <c r="C194" t="n">
         <v>69.48999786376953</v>
@@ -5549,11 +5561,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>55.08371734619141</v>
+        <v>55.08370971679688</v>
       </c>
       <c r="C195" t="n">
         <v>64.76999664306641</v>
@@ -5578,11 +5590,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>61.66621780395508</v>
+        <v>61.66620254516602</v>
       </c>
       <c r="C196" t="n">
         <v>72.51000213623047</v>
@@ -5607,7 +5619,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>64.94123077392578</v>
+        <v>64.94125366210938</v>
       </c>
       <c r="C198" t="n">
         <v>75.66000366210938</v>
@@ -5665,11 +5677,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>61.20752334594727</v>
+        <v>61.20751190185547</v>
       </c>
       <c r="C199" t="n">
         <v>71.30999755859375</v>
@@ -5694,11 +5706,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>65.99699401855469</v>
+        <v>65.99698638916016</v>
       </c>
       <c r="C200" t="n">
         <v>76.88999938964844</v>
@@ -5723,11 +5735,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>66.73403167724609</v>
+        <v>66.73403930664062</v>
       </c>
       <c r="C201" t="n">
         <v>77.06999969482422</v>
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.88040161132812</v>
+        <v>58.88040924072266</v>
       </c>
       <c r="C202" t="n">
         <v>68</v>
@@ -5781,7 +5793,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5810,11 +5822,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>59.18865966796875</v>
+        <v>59.18865585327148</v>
       </c>
       <c r="C204" t="n">
         <v>67.63999938964844</v>
@@ -5839,11 +5851,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>62.48760986328125</v>
+        <v>62.48761749267578</v>
       </c>
       <c r="C205" t="n">
         <v>71.41000366210938</v>
@@ -5868,7 +5880,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>55.75659561157227</v>
+        <v>55.756591796875</v>
       </c>
       <c r="C207" t="n">
         <v>63.06000137329102</v>
@@ -5926,11 +5938,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>61.52146530151367</v>
+        <v>61.52146911621094</v>
       </c>
       <c r="C208" t="n">
         <v>69.58000183105469</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>65.03168487548828</v>
+        <v>65.03167724609375</v>
       </c>
       <c r="C209" t="n">
         <v>73.55000305175781</v>
@@ -5984,11 +5996,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>62.25557327270508</v>
+        <v>62.25555419921875</v>
       </c>
       <c r="C210" t="n">
         <v>69.75</v>
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6042,11 +6054,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>64.56727600097656</v>
+        <v>64.5672607421875</v>
       </c>
       <c r="C212" t="n">
         <v>72.33999633789062</v>
@@ -6071,11 +6083,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>61.07905960083008</v>
+        <v>61.07905578613281</v>
       </c>
       <c r="C213" t="n">
         <v>67.73000335693359</v>
@@ -6100,11 +6112,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>58.36463928222656</v>
+        <v>58.36463165283203</v>
       </c>
       <c r="C214" t="n">
         <v>64.72000122070312</v>
@@ -6129,11 +6141,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>60.69129180908203</v>
+        <v>60.6912841796875</v>
       </c>
       <c r="C215" t="n">
         <v>67.30000305175781</v>
@@ -6158,7 +6170,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6187,11 +6199,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>63.87061309814453</v>
+        <v>63.8706169128418</v>
       </c>
       <c r="C217" t="n">
         <v>70.12000274658203</v>
@@ -6216,11 +6228,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>63.32408142089844</v>
+        <v>63.32406997680664</v>
       </c>
       <c r="C218" t="n">
         <v>69.51999664306641</v>
@@ -6245,11 +6257,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>61.90481185913086</v>
+        <v>61.90480804443359</v>
       </c>
       <c r="C219" t="n">
         <v>67.25</v>
@@ -6274,11 +6286,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>66.03792572021484</v>
+        <v>66.03793334960938</v>
       </c>
       <c r="C220" t="n">
         <v>71.73999786376953</v>
@@ -6303,11 +6315,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>67.65803527832031</v>
+        <v>67.65804290771484</v>
       </c>
       <c r="C221" t="n">
         <v>73.5</v>
@@ -6332,11 +6344,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>74.44551849365234</v>
+        <v>74.44552612304688</v>
       </c>
       <c r="C222" t="n">
         <v>80.13999938964844</v>
@@ -6361,11 +6373,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>72.05813598632812</v>
+        <v>72.05814361572266</v>
       </c>
       <c r="C223" t="n">
         <v>77.56999969482422</v>
@@ -6390,11 +6402,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>77.58535003662109</v>
+        <v>77.58534240722656</v>
       </c>
       <c r="C224" t="n">
         <v>83.51999664306641</v>
@@ -6419,11 +6431,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>80.92769622802734</v>
+        <v>80.92770385742188</v>
       </c>
       <c r="C225" t="n">
         <v>86.40000152587891</v>
@@ -6448,7 +6460,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6506,11 +6518,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>84.17401885986328</v>
+        <v>84.17402648925781</v>
       </c>
       <c r="C228" t="n">
         <v>89.12999725341797</v>
@@ -6535,11 +6547,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>77.74269866943359</v>
+        <v>77.74269104003906</v>
       </c>
       <c r="C229" t="n">
         <v>82.31999969482422</v>
@@ -6564,11 +6576,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>79.28205871582031</v>
+        <v>79.28205108642578</v>
       </c>
       <c r="C230" t="n">
         <v>83.94999694824219</v>
@@ -6593,11 +6605,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>85.51680755615234</v>
+        <v>85.51679992675781</v>
       </c>
       <c r="C231" t="n">
         <v>89.79000091552734</v>
@@ -6622,11 +6634,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>87.57399749755859</v>
+        <v>87.57400512695312</v>
       </c>
       <c r="C232" t="n">
         <v>91.94999694824219</v>
@@ -6651,11 +6663,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>87.51685333251953</v>
+        <v>87.51686859130859</v>
       </c>
       <c r="C233" t="n">
         <v>91.88999938964844</v>
@@ -6680,11 +6692,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>86.43785095214844</v>
+        <v>86.43785858154297</v>
       </c>
       <c r="C234" t="n">
         <v>90</v>
@@ -6709,7 +6721,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6738,11 +6750,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>90.74053955078125</v>
+        <v>90.74054718017578</v>
       </c>
       <c r="C236" t="n">
         <v>94.48000335693359</v>
@@ -6767,7 +6779,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6796,11 +6808,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>91.74074554443359</v>
+        <v>91.74073791503906</v>
       </c>
       <c r="C238" t="n">
         <v>94.76999664306641</v>
@@ -6825,7 +6837,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6854,11 +6866,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>88.93307495117188</v>
+        <v>88.93308258056641</v>
       </c>
       <c r="C240" t="n">
         <v>91.12000274658203</v>
@@ -6883,7 +6895,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6912,7 +6924,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6941,11 +6953,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>95.78936767578125</v>
+        <v>95.78937530517578</v>
       </c>
       <c r="C243" t="n">
         <v>97.37999725341797</v>
@@ -6970,7 +6982,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6999,11 +7011,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>95.12047576904297</v>
+        <v>95.1204833984375</v>
       </c>
       <c r="C245" t="n">
         <v>96.69999694824219</v>
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7057,7 +7069,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7086,7 +7098,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7115,7 +7127,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7144,32 +7156,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>83.47000122070312</v>
+        <v>82.88999938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>83.47000122070312</v>
+        <v>82.88999938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>99377800</v>
+        <v>104295300</v>
       </c>
       <c r="E250" t="n">
         <v>4.15</v>
       </c>
       <c r="F250" t="n">
-        <v>20.11325330619352</v>
+        <v>19.97349382883095</v>
       </c>
       <c r="G250" t="n">
         <v>1127301098</v>
       </c>
       <c r="H250" t="n">
-        <v>94095824026.15997</v>
+        <v>93441987325.17001</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08815550714561621</v>
+        <v>0.09251769574697957</v>
       </c>
     </row>
   </sheetData>
@@ -7201,75 +7213,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40052</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40052</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7431,13 +7443,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7473,13 +7485,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7506,7 +7518,7 @@
       <c r="I7" t="n">
         <v>2.06</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7519,13 +7531,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7552,7 +7564,7 @@
       <c r="I8" t="n">
         <v>2.5</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7565,13 +7577,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="I9" t="n">
         <v>2.51</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7611,13 +7623,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7644,7 +7656,7 @@
       <c r="I10" t="n">
         <v>2.49</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7657,13 +7669,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7690,7 +7702,7 @@
       <c r="I11" t="n">
         <v>2.36</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7703,13 +7715,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7736,7 +7748,7 @@
       <c r="I12" t="n">
         <v>2.25</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7749,13 +7761,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7782,7 +7794,7 @@
       <c r="I13" t="n">
         <v>2.34</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7795,13 +7807,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7828,7 +7840,7 @@
       <c r="I14" t="n">
         <v>2.43</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="K14" t="n">
@@ -7841,13 +7853,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7874,7 +7886,7 @@
       <c r="I15" t="n">
         <v>2.55</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7887,13 +7899,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7920,7 +7932,7 @@
       <c r="I16" t="n">
         <v>2.48</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K16" t="n">
@@ -7933,13 +7945,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7966,7 +7978,7 @@
       <c r="I17" t="n">
         <v>2.49</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K17" t="n">
@@ -7979,13 +7991,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8012,7 +8024,7 @@
       <c r="I18" t="n">
         <v>2.54</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -8025,13 +8037,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8058,7 +8070,7 @@
       <c r="I19" t="n">
         <v>2.67</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8071,13 +8083,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8104,7 +8116,7 @@
       <c r="I20" t="n">
         <v>2.34</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="K20" t="n">
@@ -8117,13 +8129,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8150,7 +8162,7 @@
       <c r="I21" t="n">
         <v>1.97</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K21" t="n">
@@ -8163,13 +8175,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8196,7 +8208,7 @@
       <c r="I22" t="n">
         <v>1.83</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K22" t="n">
@@ -8209,13 +8221,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8242,7 +8254,7 @@
       <c r="I23" t="n">
         <v>1.87</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8255,13 +8267,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8288,7 +8300,7 @@
       <c r="I24" t="n">
         <v>2.17</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8301,13 +8313,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8334,7 +8346,7 @@
       <c r="I25" t="n">
         <v>2.51</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K25" t="n">
@@ -8347,13 +8359,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8380,7 +8392,7 @@
       <c r="I26" t="n">
         <v>2.34</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K26" t="n">
@@ -8393,13 +8405,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8426,7 +8438,7 @@
       <c r="I27" t="n">
         <v>2.18</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K27" t="n">
@@ -8439,13 +8451,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8472,7 +8484,7 @@
       <c r="I28" t="n">
         <v>2.35</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K28" t="n">
@@ -8485,13 +8497,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8518,7 +8530,7 @@
       <c r="I29" t="n">
         <v>2.36</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K29" t="n">
@@ -8531,13 +8543,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8564,7 +8576,7 @@
       <c r="I30" t="n">
         <v>2.61</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K30" t="n">
@@ -8577,13 +8589,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8610,7 +8622,7 @@
       <c r="I31" t="n">
         <v>2.6</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8623,13 +8635,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8656,7 +8668,7 @@
       <c r="I32" t="n">
         <v>2.57</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8669,13 +8681,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8702,7 +8714,7 @@
       <c r="I33" t="n">
         <v>2.53</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="K33" t="n">
@@ -8715,13 +8727,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8748,7 +8760,7 @@
       <c r="I34" t="n">
         <v>2.64</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K34" t="n">
@@ -8761,13 +8773,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8794,7 +8806,7 @@
       <c r="I35" t="n">
         <v>2.54</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K35" t="n">
@@ -8807,13 +8819,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8840,7 +8852,7 @@
       <c r="I36" t="n">
         <v>2.67</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8853,13 +8865,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8886,7 +8898,7 @@
       <c r="I37" t="n">
         <v>0.6499999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8899,13 +8911,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8932,7 +8944,7 @@
       <c r="I38" t="n">
         <v>0.5499999999999998</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8945,13 +8957,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8978,7 +8990,7 @@
       <c r="I39" t="n">
         <v>0.8399999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K39" t="n">
@@ -8991,13 +9003,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9024,7 +9036,7 @@
       <c r="I40" t="n">
         <v>1.1</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9037,13 +9049,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9070,7 +9082,7 @@
       <c r="I41" t="n">
         <v>2.32</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K41" t="n">
@@ -9083,13 +9095,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9116,7 +9128,7 @@
       <c r="I42" t="n">
         <v>2.39</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K42" t="n">
@@ -9129,13 +9141,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9162,7 +9174,7 @@
       <c r="I43" t="n">
         <v>2.17</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="K43" t="n">
@@ -9175,13 +9187,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9208,7 +9220,7 @@
       <c r="I44" t="n">
         <v>3.24</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9221,13 +9233,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9254,7 +9266,7 @@
       <c r="I45" t="n">
         <v>4.239999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9267,13 +9279,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9300,7 +9312,7 @@
       <c r="I46" t="n">
         <v>4.359999999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K46" t="n">
@@ -9313,13 +9325,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9346,7 +9358,7 @@
       <c r="I47" t="n">
         <v>4.510000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K47" t="n">
@@ -9359,13 +9371,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9392,7 +9404,7 @@
       <c r="I48" t="n">
         <v>3.33</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K48" t="n">
@@ -9405,13 +9417,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9438,7 +9450,7 @@
       <c r="I49" t="n">
         <v>3.06</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K49" t="n">
@@ -9451,13 +9463,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9484,7 +9496,7 @@
       <c r="I50" t="n">
         <v>2.99</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9497,13 +9509,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9530,7 +9542,7 @@
       <c r="I51" t="n">
         <v>2.93</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="K51" t="n">
@@ -9543,13 +9555,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9576,7 +9588,7 @@
       <c r="I52" t="n">
         <v>3.18</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9589,13 +9601,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9622,7 +9634,7 @@
       <c r="I53" t="n">
         <v>2.95</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9635,13 +9647,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9668,7 +9680,7 @@
       <c r="I54" t="n">
         <v>2.8</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K54" t="n">
@@ -9681,13 +9693,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9714,7 +9726,7 @@
       <c r="I55" t="n">
         <v>2.24</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K55" t="n">
@@ -9727,13 +9739,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9760,7 +9772,7 @@
       <c r="I56" t="n">
         <v>2.149999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9773,13 +9785,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9806,7 +9818,7 @@
       <c r="I57" t="n">
         <v>2.83</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9819,13 +9831,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9852,7 +9864,7 @@
       <c r="I58" t="n">
         <v>3.15</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9865,13 +9877,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9898,7 +9910,7 @@
       <c r="I59" t="n">
         <v>3.26</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K59" t="n">
@@ -9911,13 +9923,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9944,7 +9956,7 @@
       <c r="I60" t="n">
         <v>3.08</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9957,13 +9969,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9990,7 +10002,7 @@
       <c r="I61" t="n">
         <v>2.81</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -10003,13 +10015,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10036,7 +10048,7 @@
       <c r="I62" t="n">
         <v>2.75</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -10049,13 +10061,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10082,7 +10094,7 @@
       <c r="I63" t="n">
         <v>3.62</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K63" t="n">
@@ -10095,13 +10107,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10128,7 +10140,7 @@
       <c r="I64" t="n">
         <v>3.86</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10141,13 +10153,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10174,7 +10186,7 @@
       <c r="I65" t="n">
         <v>4.19</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10187,13 +10199,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10220,7 +10232,7 @@
       <c r="I66" t="n">
         <v>4.290000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10233,13 +10245,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10266,7 +10278,7 @@
       <c r="I67" t="n">
         <v>3.990000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K67" t="n">
@@ -10279,13 +10291,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10312,7 +10324,7 @@
       <c r="I68" t="n">
         <v>4.17</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10325,13 +10337,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10358,7 +10370,7 @@
       <c r="I69" t="n">
         <v>3.870000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10371,13 +10383,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10404,7 +10416,7 @@
       <c r="I70" t="n">
         <v>4.02</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10417,13 +10429,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10450,7 +10462,7 @@
       <c r="I71" t="n">
         <v>3.92</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10463,13 +10475,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10496,7 +10508,7 @@
       <c r="I72" t="n">
         <v>3.91</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10509,13 +10521,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10536,7 +10548,7 @@
       <c r="I73" t="n">
         <v>4.15</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K73" t="n">
@@ -10573,52 +10585,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40052</v>
       </c>
       <c r="C2" t="n">
@@ -10647,10 +10659,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="C11" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C13" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C15" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="C17" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C19" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C22" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C23" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C24" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C25" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C28" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="C30" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C31" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C32" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C36" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C38" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C39" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="C40" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C45" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C46" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C47" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="C48" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C51" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C52" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C54" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C55" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C56" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C60" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C64" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C66" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C67" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12809,12 +12821,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SO.xlsx
+++ b/salidas/empresas/SO.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.94898891448975</v>
+        <v>13.94898319244385</v>
       </c>
       <c r="C2" t="n">
         <v>34.79999923706055</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78856468200684</v>
+        <v>13.78856563568115</v>
       </c>
       <c r="C3" t="n">
         <v>34.02999877929688</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.2780237197876</v>
+        <v>13.2780294418335</v>
       </c>
       <c r="C4" t="n">
         <v>32.77000045776367</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.22130489349365</v>
+        <v>13.22130680084229</v>
       </c>
       <c r="C5" t="n">
         <v>32.22999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.11464691162109</v>
+        <v>13.11464500427246</v>
       </c>
       <c r="C6" t="n">
         <v>31.96999931335449</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.14746570587158</v>
+        <v>13.14746475219727</v>
       </c>
       <c r="C7" t="n">
         <v>32.04999923706055</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85714626312256</v>
+        <v>13.85713863372803</v>
       </c>
       <c r="C8" t="n">
         <v>33.77999877929688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.21947574615479</v>
+        <v>14.21946811676025</v>
       </c>
       <c r="C9" t="n">
         <v>34.27000045776367</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.29830169677734</v>
+        <v>14.29830360412598</v>
       </c>
       <c r="C10" t="n">
         <v>34.45999908447266</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10326480865479</v>
+        <v>15.1032600402832</v>
       </c>
       <c r="C11" t="n">
         <v>36.40000152587891</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>15.20213413238525</v>
+        <v>15.2021369934082</v>
       </c>
       <c r="C12" t="n">
         <v>36.25</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>15.45794582366943</v>
+        <v>15.4579553604126</v>
       </c>
       <c r="C13" t="n">
         <v>36.86000061035156</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>15.31956100463867</v>
+        <v>15.31955909729004</v>
       </c>
       <c r="C14" t="n">
         <v>36.52999877929688</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>15.17459774017334</v>
+        <v>15.17459201812744</v>
       </c>
       <c r="C15" t="n">
         <v>35.79999923706055</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>15.53488063812256</v>
+        <v>15.53488826751709</v>
       </c>
       <c r="C16" t="n">
         <v>36.65000152587891</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>16.01809883117676</v>
+        <v>16.01810264587402</v>
       </c>
       <c r="C17" t="n">
         <v>37.79000091552734</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.42695426940918</v>
+        <v>15.42695236206055</v>
       </c>
       <c r="C18" t="n">
         <v>36.0099983215332</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.69009590148926</v>
+        <v>14.69009399414062</v>
       </c>
       <c r="C19" t="n">
         <v>34.29000091552734</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.41163063049316</v>
+        <v>14.41163444519043</v>
       </c>
       <c r="C20" t="n">
         <v>33.63999938964844</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.38175296783447</v>
+        <v>15.38174819946289</v>
       </c>
       <c r="C21" t="n">
         <v>35.4900016784668</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.72414016723633</v>
+        <v>15.72414112091064</v>
       </c>
       <c r="C22" t="n">
         <v>36.27999877929688</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.88884162902832</v>
+        <v>15.88883781433105</v>
       </c>
       <c r="C23" t="n">
         <v>36.65999984741211</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.98133659362793</v>
+        <v>16.9813404083252</v>
       </c>
       <c r="C25" t="n">
         <v>38.75</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>16.11684799194336</v>
+        <v>16.11684226989746</v>
       </c>
       <c r="C26" t="n">
         <v>36.36999893188477</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>15.30147933959961</v>
+        <v>15.30148220062256</v>
       </c>
       <c r="C27" t="n">
         <v>34.52999877929688</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.78006553649902</v>
+        <v>15.78006267547607</v>
       </c>
       <c r="C28" t="n">
         <v>35.61000061035156</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.49794769287109</v>
+        <v>16.49794006347656</v>
       </c>
       <c r="C29" t="n">
         <v>37.22999954223633</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.22455596923828</v>
+        <v>16.22454261779785</v>
       </c>
       <c r="C30" t="n">
         <v>36.20000076293945</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.65085887908936</v>
+        <v>15.65086269378662</v>
       </c>
       <c r="C31" t="n">
         <v>34.91999816894531</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>16.04943466186523</v>
+        <v>16.04943084716797</v>
       </c>
       <c r="C32" t="n">
         <v>35.38999938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.0108585357666</v>
+        <v>17.01085662841797</v>
       </c>
       <c r="C33" t="n">
         <v>37.5099983215332</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.09248733520508</v>
+        <v>17.09249305725098</v>
       </c>
       <c r="C34" t="n">
         <v>37.68999862670898</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.76355934143066</v>
+        <v>15.7635669708252</v>
       </c>
       <c r="C35" t="n">
         <v>34.34000015258789</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>16.67246627807617</v>
+        <v>16.67246437072754</v>
       </c>
       <c r="C36" t="n">
         <v>36.31999969482422</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.98462104797363</v>
+        <v>16.984619140625</v>
       </c>
       <c r="C37" t="n">
         <v>37</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.54497337341309</v>
+        <v>15.54497146606445</v>
       </c>
       <c r="C38" t="n">
         <v>33.45000076293945</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.08573818206787</v>
+        <v>14.0857400894165</v>
       </c>
       <c r="C39" t="n">
         <v>30.30999946594238</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.229811668396</v>
+        <v>14.22980308532715</v>
       </c>
       <c r="C40" t="n">
         <v>30.6200008392334</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.61984252929688</v>
+        <v>13.61984062194824</v>
       </c>
       <c r="C41" t="n">
         <v>28.8799991607666</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>13.39818954467773</v>
+        <v>13.3981876373291</v>
       </c>
       <c r="C42" t="n">
         <v>28.40999984741211</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.69508934020996</v>
+        <v>14.69509124755859</v>
       </c>
       <c r="C43" t="n">
         <v>31.15999984741211</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>15.01501655578613</v>
+        <v>15.01502323150635</v>
       </c>
       <c r="C44" t="n">
         <v>31.39999961853027</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>14.91937828063965</v>
+        <v>14.91938877105713</v>
       </c>
       <c r="C45" t="n">
         <v>31.20000076293945</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.14412975311279</v>
+        <v>15.14413261413574</v>
       </c>
       <c r="C46" t="n">
         <v>31.67000007629395</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.1181583404541</v>
+        <v>15.1181640625</v>
       </c>
       <c r="C47" t="n">
         <v>31.19000053405762</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.55440330505371</v>
+        <v>15.55439758300781</v>
       </c>
       <c r="C48" t="n">
         <v>32.09000015258789</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>16.15059280395508</v>
+        <v>16.15059661865234</v>
       </c>
       <c r="C49" t="n">
         <v>33.31999969482422</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.71999359130859</v>
+        <v>15.71999263763428</v>
       </c>
       <c r="C50" t="n">
         <v>32</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.60700416564941</v>
+        <v>15.60700702667236</v>
       </c>
       <c r="C51" t="n">
         <v>31.77000045776367</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.28984069824219</v>
+        <v>16.28984832763672</v>
       </c>
       <c r="C52" t="n">
         <v>33.15999984741211</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.19954299926758</v>
+        <v>17.19954109191895</v>
       </c>
       <c r="C53" t="n">
         <v>34.56000137329102</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.27387046813965</v>
+        <v>16.27386665344238</v>
       </c>
       <c r="C54" t="n">
         <v>32.70000076293945</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.5625171661377</v>
+        <v>16.56251335144043</v>
       </c>
       <c r="C55" t="n">
         <v>33.27999877929688</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.80413627624512</v>
+        <v>17.80414390563965</v>
       </c>
       <c r="C56" t="n">
         <v>35.33000183105469</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>18.48950004577637</v>
+        <v>18.4894962310791</v>
       </c>
       <c r="C57" t="n">
         <v>36.68999862670898</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.76667213439941</v>
+        <v>18.76667022705078</v>
       </c>
       <c r="C58" t="n">
         <v>37.2400016784668</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>19.31358909606934</v>
+        <v>19.31358528137207</v>
       </c>
       <c r="C59" t="n">
         <v>37.86999893188477</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.23709106445312</v>
+        <v>19.23709487915039</v>
       </c>
       <c r="C60" t="n">
         <v>37.72000122070312</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.49718856811523</v>
+        <v>19.4971866607666</v>
       </c>
       <c r="C61" t="n">
         <v>38.22999954223633</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>19.67394256591797</v>
+        <v>19.6739387512207</v>
       </c>
       <c r="C63" t="n">
         <v>38.11000061035156</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.67394256591797</v>
+        <v>19.6739387512207</v>
       </c>
       <c r="C64" t="n">
         <v>38.11000061035156</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>20.40205764770508</v>
+        <v>20.40205001831055</v>
       </c>
       <c r="C65" t="n">
         <v>39.04000091552734</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>20.94554901123047</v>
+        <v>20.945556640625</v>
       </c>
       <c r="C66" t="n">
         <v>40.08000183105469</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>20.90937232971191</v>
+        <v>20.90938186645508</v>
       </c>
       <c r="C68" t="n">
         <v>39.54000091552734</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>21.87182998657227</v>
+        <v>21.8718204498291</v>
       </c>
       <c r="C69" t="n">
         <v>41.36000061035156</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.40592384338379</v>
+        <v>22.40591812133789</v>
       </c>
       <c r="C70" t="n">
         <v>42.36999893188477</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.8448371887207</v>
+        <v>22.84483337402344</v>
       </c>
       <c r="C71" t="n">
         <v>43.20000076293945</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>23.47718048095703</v>
+        <v>23.47718238830566</v>
       </c>
       <c r="C72" t="n">
         <v>43.90999984741211</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>24.74967575073242</v>
+        <v>24.74967765808105</v>
       </c>
       <c r="C73" t="n">
         <v>46.29000091552734</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>24.3593692779541</v>
+        <v>24.35937881469727</v>
       </c>
       <c r="C74" t="n">
         <v>45.56000137329102</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>23.8757438659668</v>
+        <v>23.87573623657227</v>
       </c>
       <c r="C75" t="n">
         <v>44.18999862670898</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.82126235961914</v>
+        <v>24.82126045227051</v>
       </c>
       <c r="C77" t="n">
         <v>45.93999862670898</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>25.07271003723145</v>
+        <v>25.07272529602051</v>
       </c>
       <c r="C78" t="n">
         <v>45.90999984741211</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.29604339599609</v>
+        <v>26.29603958129883</v>
       </c>
       <c r="C80" t="n">
         <v>48.15000152587891</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.01187896728516</v>
+        <v>25.01187705993652</v>
       </c>
       <c r="C81" t="n">
         <v>45.33000183105469</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.43121528625488</v>
+        <v>25.43122482299805</v>
       </c>
       <c r="C82" t="n">
         <v>46.09000015258789</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.84505844116211</v>
+        <v>25.84506225585938</v>
       </c>
       <c r="C83" t="n">
         <v>46.84000015258789</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.28376007080078</v>
+        <v>24.28374671936035</v>
       </c>
       <c r="C84" t="n">
         <v>43.54999923706055</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>23.87112998962402</v>
+        <v>23.87112808227539</v>
       </c>
       <c r="C85" t="n">
         <v>42.81000137329102</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.93733406066895</v>
+        <v>24.93733215332031</v>
       </c>
       <c r="C86" t="n">
         <v>44.22999954223633</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.37709999084473</v>
+        <v>25.37710762023926</v>
       </c>
       <c r="C87" t="n">
         <v>45.0099983215332</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.45397758483887</v>
+        <v>26.45398330688477</v>
       </c>
       <c r="C88" t="n">
         <v>46.91999816894531</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>27.19257354736328</v>
+        <v>27.19257164001465</v>
       </c>
       <c r="C89" t="n">
         <v>48.22999954223633</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.01639366149902</v>
+        <v>25.01640129089355</v>
       </c>
       <c r="C90" t="n">
         <v>43.90000152587891</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.14746856689453</v>
+        <v>25.14746284484863</v>
       </c>
       <c r="C91" t="n">
         <v>44.13000106811523</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>25.55205726623535</v>
+        <v>25.55205917358398</v>
       </c>
       <c r="C92" t="n">
         <v>44.84000015258789</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.98837089538574</v>
+        <v>23.98836898803711</v>
       </c>
       <c r="C93" t="n">
         <v>41.61999893188477</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>23.73476600646973</v>
+        <v>23.73476791381836</v>
       </c>
       <c r="C94" t="n">
         <v>41.18000030517578</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>23.86796379089355</v>
+        <v>23.86795806884766</v>
       </c>
       <c r="C95" t="n">
         <v>40.90999984741211</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>23.70460319519043</v>
+        <v>23.70459938049316</v>
       </c>
       <c r="C96" t="n">
         <v>40.63000106811523</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>23.98464393615723</v>
+        <v>23.98464012145996</v>
       </c>
       <c r="C97" t="n">
         <v>41.11000061035156</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>24.36257171630859</v>
+        <v>24.36256980895996</v>
       </c>
       <c r="C98" t="n">
         <v>41.2400016784668</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>25.95758247375488</v>
+        <v>25.95758819580078</v>
       </c>
       <c r="C100" t="n">
         <v>43.93999862670898</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>26.16278076171875</v>
+        <v>26.16277694702148</v>
       </c>
       <c r="C102" t="n">
         <v>43.77999877929688</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>27.11893081665039</v>
+        <v>27.11892700195312</v>
       </c>
       <c r="C103" t="n">
         <v>45.38000106811523</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>26.17965316772461</v>
+        <v>26.17964935302734</v>
       </c>
       <c r="C104" t="n">
         <v>43.29000091552734</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>26.85092735290527</v>
+        <v>26.85093688964844</v>
       </c>
       <c r="C105" t="n">
         <v>44.40000152587891</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>26.39735984802246</v>
+        <v>26.39736175537109</v>
       </c>
       <c r="C106" t="n">
         <v>43.65000152587891</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.35693740844727</v>
+        <v>28.3569450378418</v>
       </c>
       <c r="C107" t="n">
         <v>46.36000061035156</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.01144218444824</v>
+        <v>29.01143455505371</v>
       </c>
       <c r="C108" t="n">
         <v>47.43000030517578</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.03903770446777</v>
+        <v>30.03903007507324</v>
       </c>
       <c r="C109" t="n">
         <v>49.11000061035156</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.02382469177246</v>
+        <v>31.02381896972656</v>
       </c>
       <c r="C110" t="n">
         <v>50.72000122070312</v>
@@ -3149,7 +3149,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>28.31834983825684</v>
+        <v>28.31836128234863</v>
       </c>
       <c r="C111" t="n">
         <v>45.79000091552734</v>
@@ -3174,7 +3174,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>27.38449859619141</v>
+        <v>27.38451194763184</v>
       </c>
       <c r="C112" t="n">
         <v>44.27999877929688</v>
@@ -3232,7 +3232,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>27.36211395263672</v>
+        <v>27.36212539672852</v>
       </c>
       <c r="C114" t="n">
         <v>43.68999862670898</v>
@@ -3261,7 +3261,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>26.2410831451416</v>
+        <v>26.24109077453613</v>
       </c>
       <c r="C115" t="n">
         <v>41.90000152587891</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.01345634460449</v>
+        <v>28.01344871520996</v>
       </c>
       <c r="C116" t="n">
         <v>44.72999954223633</v>
@@ -3319,7 +3319,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.50749778747559</v>
+        <v>27.50750350952148</v>
       </c>
       <c r="C117" t="n">
         <v>43.40999984741211</v>
@@ -3348,7 +3348,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.32493782043457</v>
+        <v>28.3249340057373</v>
       </c>
       <c r="C118" t="n">
         <v>44.70000076293945</v>
@@ -3402,7 +3402,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>28.56804084777832</v>
+        <v>28.56803894042969</v>
       </c>
       <c r="C120" t="n">
         <v>44.54000091552734</v>
@@ -3427,7 +3427,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.01119041442871</v>
+        <v>30.01119613647461</v>
       </c>
       <c r="C121" t="n">
         <v>46.79000091552734</v>
@@ -3452,7 +3452,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.37737846374512</v>
+        <v>31.37738227844238</v>
       </c>
       <c r="C122" t="n">
         <v>48.91999816894531</v>
@@ -3477,7 +3477,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.24752616882324</v>
+        <v>31.24752426147461</v>
       </c>
       <c r="C123" t="n">
         <v>48.18000030517578</v>
@@ -3506,7 +3506,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>33.5499153137207</v>
+        <v>33.54991912841797</v>
       </c>
       <c r="C124" t="n">
         <v>51.72999954223633</v>
@@ -3535,7 +3535,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.49277114868164</v>
+        <v>32.49276733398438</v>
       </c>
       <c r="C125" t="n">
         <v>50.09999847412109</v>
@@ -3564,7 +3564,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.42557525634766</v>
+        <v>32.42557144165039</v>
       </c>
       <c r="C126" t="n">
         <v>49.43999862670898</v>
@@ -3622,7 +3622,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.08835220336914</v>
+        <v>35.08834838867188</v>
       </c>
       <c r="C128" t="n">
         <v>53.5</v>
@@ -3680,7 +3680,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>34.00559997558594</v>
+        <v>34.00558853149414</v>
       </c>
       <c r="C130" t="n">
         <v>51.29999923706055</v>
@@ -3767,7 +3767,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.98836898803711</v>
+        <v>32.98836135864258</v>
       </c>
       <c r="C133" t="n">
         <v>49.18999862670898</v>
@@ -3796,7 +3796,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>33.14931488037109</v>
+        <v>33.14933395385742</v>
       </c>
       <c r="C134" t="n">
         <v>49.43000030517578</v>
@@ -3825,7 +3825,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.48085403442383</v>
+        <v>34.48086929321289</v>
       </c>
       <c r="C135" t="n">
         <v>50.81999969482422</v>
@@ -3854,7 +3854,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>33.77522659301758</v>
+        <v>33.77524566650391</v>
       </c>
       <c r="C136" t="n">
         <v>49.77999877929688</v>
@@ -3883,7 +3883,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.78880310058594</v>
+        <v>33.78879928588867</v>
       </c>
       <c r="C137" t="n">
         <v>49.79999923706055</v>
@@ -3912,7 +3912,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>34.7424430847168</v>
+        <v>34.74243927001953</v>
       </c>
       <c r="C138" t="n">
         <v>50.61000061035156</v>
@@ -3941,7 +3941,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>32.86836242675781</v>
+        <v>32.86837387084961</v>
       </c>
       <c r="C139" t="n">
         <v>47.88000106811523</v>
@@ -4028,7 +4028,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>34.13748550415039</v>
+        <v>34.13748168945312</v>
       </c>
       <c r="C142" t="n">
         <v>49.13999938964844</v>
@@ -4057,7 +4057,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>36.26325988769531</v>
+        <v>36.26327133178711</v>
       </c>
       <c r="C143" t="n">
         <v>52.20000076293945</v>
@@ -4115,7 +4115,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>33.78532409667969</v>
+        <v>33.78531646728516</v>
       </c>
       <c r="C145" t="n">
         <v>48.09000015258789</v>
@@ -4144,7 +4144,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.69174194335938</v>
+        <v>31.69174957275391</v>
       </c>
       <c r="C146" t="n">
         <v>45.11000061035156</v>
@@ -4173,7 +4173,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.65048599243164</v>
+        <v>30.65048980712891</v>
       </c>
       <c r="C147" t="n">
         <v>43.06000137329102</v>
@@ -4202,7 +4202,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>31.78937339782715</v>
+        <v>31.78937149047852</v>
       </c>
       <c r="C148" t="n">
         <v>44.65999984741211</v>
@@ -4231,7 +4231,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>32.82860946655273</v>
+        <v>32.82861709594727</v>
       </c>
       <c r="C149" t="n">
         <v>46.11999893188477</v>
@@ -4260,7 +4260,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>32.40595626831055</v>
+        <v>32.40595245361328</v>
       </c>
       <c r="C150" t="n">
         <v>44.90000152587891</v>
@@ -4289,7 +4289,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.42361068725586</v>
+        <v>33.42361450195312</v>
       </c>
       <c r="C151" t="n">
         <v>46.31000137329102</v>
@@ -4318,7 +4318,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>35.07638168334961</v>
+        <v>35.07637023925781</v>
       </c>
       <c r="C152" t="n">
         <v>48.59999847412109</v>
@@ -4347,7 +4347,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>32.00184631347656</v>
+        <v>32.0018424987793</v>
       </c>
       <c r="C153" t="n">
         <v>43.77999877929688</v>
@@ -4376,7 +4376,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>31.87027740478516</v>
+        <v>31.87026596069336</v>
       </c>
       <c r="C154" t="n">
         <v>43.59999847412109</v>
@@ -4405,7 +4405,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>32.91555786132812</v>
+        <v>32.91555404663086</v>
       </c>
       <c r="C155" t="n">
         <v>45.02999877929688</v>
@@ -4434,7 +4434,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.04243850708008</v>
+        <v>35.04243469238281</v>
       </c>
       <c r="C156" t="n">
         <v>47.33000183105469</v>
@@ -4463,7 +4463,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>32.51770782470703</v>
+        <v>32.5177116394043</v>
       </c>
       <c r="C157" t="n">
         <v>43.91999816894531</v>
@@ -4492,7 +4492,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>35.98271179199219</v>
+        <v>35.98270797729492</v>
       </c>
       <c r="C158" t="n">
         <v>48.59999847412109</v>
@@ -4521,7 +4521,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>37.24393844604492</v>
+        <v>37.24393081665039</v>
       </c>
       <c r="C159" t="n">
         <v>49.68999862670898</v>
@@ -4550,7 +4550,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>38.73548889160156</v>
+        <v>38.73549652099609</v>
       </c>
       <c r="C160" t="n">
         <v>51.68000030517578</v>
@@ -4579,7 +4579,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.8897590637207</v>
+        <v>39.88976287841797</v>
       </c>
       <c r="C161" t="n">
         <v>53.22000122070312</v>
@@ -4637,7 +4637,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>41.91448593139648</v>
+        <v>41.91448974609375</v>
       </c>
       <c r="C163" t="n">
         <v>55.27999877929688</v>
@@ -4666,7 +4666,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.6120491027832</v>
+        <v>42.61205673217773</v>
       </c>
       <c r="C164" t="n">
         <v>56.20000076293945</v>
@@ -4724,7 +4724,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>47.34470367431641</v>
+        <v>47.34469604492188</v>
       </c>
       <c r="C166" t="n">
         <v>61.77000045776367</v>
@@ -4753,7 +4753,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>48.02685165405273</v>
+        <v>48.02684783935547</v>
       </c>
       <c r="C167" t="n">
         <v>62.65999984741211</v>
@@ -4782,7 +4782,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>47.99021530151367</v>
+        <v>47.9902229309082</v>
       </c>
       <c r="C168" t="n">
         <v>61.9900016784668</v>
@@ -4811,7 +4811,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>49.31403732299805</v>
+        <v>49.31404113769531</v>
       </c>
       <c r="C169" t="n">
         <v>63.70000076293945</v>
@@ -4840,7 +4840,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>54.50091934204102</v>
+        <v>54.50089645385742</v>
       </c>
       <c r="C170" t="n">
         <v>70.40000152587891</v>
@@ -4869,7 +4869,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>47.1486930847168</v>
+        <v>47.14870834350586</v>
       </c>
       <c r="C171" t="n">
         <v>60.36000061035156</v>
@@ -4898,7 +4898,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>42.29010391235352</v>
+        <v>42.29010009765625</v>
       </c>
       <c r="C172" t="n">
         <v>54.13999938964844</v>
@@ -4927,7 +4927,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>44.31321716308594</v>
+        <v>44.31322479248047</v>
       </c>
       <c r="C173" t="n">
         <v>56.72999954223633</v>
@@ -4956,7 +4956,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>45.1060676574707</v>
+        <v>45.10607528686523</v>
       </c>
       <c r="C174" t="n">
         <v>57.06999969482422</v>
@@ -4985,7 +4985,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>40.98036956787109</v>
+        <v>40.98036575317383</v>
       </c>
       <c r="C175" t="n">
         <v>51.84999847412109</v>
@@ -5014,7 +5014,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>43.16177368164062</v>
+        <v>43.16176986694336</v>
       </c>
       <c r="C176" t="n">
         <v>54.61000061035156</v>
@@ -5043,7 +5043,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>41.72665405273438</v>
+        <v>41.72664260864258</v>
       </c>
       <c r="C177" t="n">
         <v>52.18000030517578</v>
@@ -5072,7 +5072,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>43.35796737670898</v>
+        <v>43.35796356201172</v>
       </c>
       <c r="C178" t="n">
         <v>54.22000122070312</v>
@@ -5101,7 +5101,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>45.94089126586914</v>
+        <v>45.94089889526367</v>
       </c>
       <c r="C179" t="n">
         <v>57.45000076293945</v>
@@ -5130,7 +5130,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>48.34722518920898</v>
+        <v>48.34722137451172</v>
       </c>
       <c r="C180" t="n">
         <v>59.84999847412109</v>
@@ -5159,7 +5159,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>49.62356567382812</v>
+        <v>49.62355804443359</v>
       </c>
       <c r="C181" t="n">
         <v>61.43000030517578</v>
@@ -5188,7 +5188,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>47.59596252441406</v>
+        <v>47.59596633911133</v>
       </c>
       <c r="C182" t="n">
         <v>58.91999816894531</v>
@@ -5246,7 +5246,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>50.74312210083008</v>
+        <v>50.74311065673828</v>
       </c>
       <c r="C184" t="n">
         <v>62.15999984741211</v>
@@ -5275,7 +5275,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>54.01660919189453</v>
+        <v>54.01660537719727</v>
       </c>
       <c r="C185" t="n">
         <v>66.16999816894531</v>
@@ -5304,7 +5304,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>52.7091178894043</v>
+        <v>52.70911026000977</v>
       </c>
       <c r="C186" t="n">
         <v>63.91999816894531</v>
@@ -5333,7 +5333,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>49.89719009399414</v>
+        <v>49.89718627929688</v>
       </c>
       <c r="C187" t="n">
         <v>60.5099983215332</v>
@@ -5362,7 +5362,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>52.66788482666016</v>
+        <v>52.66788864135742</v>
       </c>
       <c r="C188" t="n">
         <v>63.86999893188477</v>
@@ -5391,7 +5391,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>54.75151824951172</v>
+        <v>54.75152206420898</v>
       </c>
       <c r="C189" t="n">
         <v>65.73000335693359</v>
@@ -5420,7 +5420,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>51.61952209472656</v>
+        <v>51.61952590942383</v>
       </c>
       <c r="C190" t="n">
         <v>61.97000122070312</v>
@@ -5449,7 +5449,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>51.91106796264648</v>
+        <v>51.91106414794922</v>
       </c>
       <c r="C191" t="n">
         <v>62.31999969482422</v>
@@ -5478,7 +5478,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>51.4332275390625</v>
+        <v>51.43322372436523</v>
       </c>
       <c r="C192" t="n">
         <v>61.09999847412109</v>
@@ -5507,7 +5507,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>57.72979354858398</v>
+        <v>57.72980117797852</v>
       </c>
       <c r="C193" t="n">
         <v>68.58000183105469</v>
@@ -5536,7 +5536,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.49583435058594</v>
+        <v>58.49582672119141</v>
       </c>
       <c r="C194" t="n">
         <v>69.48999786376953</v>
@@ -5565,7 +5565,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>55.08370971679688</v>
+        <v>55.08370590209961</v>
       </c>
       <c r="C195" t="n">
         <v>64.76999664306641</v>
@@ -5594,7 +5594,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>61.66620254516602</v>
+        <v>61.66621017456055</v>
       </c>
       <c r="C196" t="n">
         <v>72.51000213623047</v>
@@ -5652,7 +5652,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>64.94125366210938</v>
+        <v>64.94124603271484</v>
       </c>
       <c r="C198" t="n">
         <v>75.66000366210938</v>
@@ -5681,7 +5681,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>61.20751190185547</v>
+        <v>61.20750427246094</v>
       </c>
       <c r="C199" t="n">
         <v>71.30999755859375</v>
@@ -5710,7 +5710,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>65.99698638916016</v>
+        <v>65.99697875976562</v>
       </c>
       <c r="C200" t="n">
         <v>76.88999938964844</v>
@@ -5739,7 +5739,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>66.73403930664062</v>
+        <v>66.73402404785156</v>
       </c>
       <c r="C201" t="n">
         <v>77.06999969482422</v>
@@ -5768,7 +5768,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>58.88040924072266</v>
+        <v>58.88040161132812</v>
       </c>
       <c r="C202" t="n">
         <v>68</v>
@@ -5797,7 +5797,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>56.6983757019043</v>
+        <v>56.69837188720703</v>
       </c>
       <c r="C203" t="n">
         <v>65.48000335693359</v>
@@ -5826,7 +5826,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>59.18865585327148</v>
+        <v>59.18865203857422</v>
       </c>
       <c r="C204" t="n">
         <v>67.63999938964844</v>
@@ -5855,7 +5855,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>62.48761749267578</v>
+        <v>62.48761367797852</v>
       </c>
       <c r="C205" t="n">
         <v>71.41000366210938</v>
@@ -5884,7 +5884,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>59.22366714477539</v>
+        <v>59.22365951538086</v>
       </c>
       <c r="C206" t="n">
         <v>67.68000030517578</v>
@@ -5913,7 +5913,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>55.756591796875</v>
+        <v>55.75659942626953</v>
       </c>
       <c r="C207" t="n">
         <v>63.06000137329102</v>
@@ -5942,7 +5942,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>61.52146911621094</v>
+        <v>61.521484375</v>
       </c>
       <c r="C208" t="n">
         <v>69.58000183105469</v>
@@ -5971,7 +5971,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>65.03167724609375</v>
+        <v>65.03169250488281</v>
       </c>
       <c r="C209" t="n">
         <v>73.55000305175781</v>
@@ -6000,7 +6000,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>62.25555419921875</v>
+        <v>62.25556182861328</v>
       </c>
       <c r="C210" t="n">
         <v>69.75</v>
@@ -6029,7 +6029,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>62.70183944702148</v>
+        <v>62.70183181762695</v>
       </c>
       <c r="C211" t="n">
         <v>70.25</v>
@@ -6087,7 +6087,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>61.07905578613281</v>
+        <v>61.07905197143555</v>
       </c>
       <c r="C213" t="n">
         <v>67.73000335693359</v>
@@ -6145,7 +6145,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>60.6912841796875</v>
+        <v>60.69128799438477</v>
       </c>
       <c r="C215" t="n">
         <v>67.30000305175781</v>
@@ -6203,7 +6203,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>63.8706169128418</v>
+        <v>63.87062454223633</v>
       </c>
       <c r="C217" t="n">
         <v>70.12000274658203</v>
@@ -6232,7 +6232,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>63.32406997680664</v>
+        <v>63.32407760620117</v>
       </c>
       <c r="C218" t="n">
         <v>69.51999664306641</v>
@@ -6261,7 +6261,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>61.90480804443359</v>
+        <v>61.90481185913086</v>
       </c>
       <c r="C219" t="n">
         <v>67.25</v>
@@ -6348,7 +6348,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>74.44552612304688</v>
+        <v>74.44553375244141</v>
       </c>
       <c r="C222" t="n">
         <v>80.13999938964844</v>
@@ -6377,7 +6377,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>72.05814361572266</v>
+        <v>72.05813598632812</v>
       </c>
       <c r="C223" t="n">
         <v>77.56999969482422</v>
@@ -6406,7 +6406,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>77.58534240722656</v>
+        <v>77.58535003662109</v>
       </c>
       <c r="C224" t="n">
         <v>83.51999664306641</v>
@@ -6464,7 +6464,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>84.46827697753906</v>
+        <v>84.46829223632812</v>
       </c>
       <c r="C226" t="n">
         <v>90.18000030517578</v>
@@ -6493,7 +6493,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>85.26445007324219</v>
+        <v>85.26444244384766</v>
       </c>
       <c r="C227" t="n">
         <v>91.02999877929688</v>
@@ -6522,7 +6522,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>84.17402648925781</v>
+        <v>84.17401885986328</v>
       </c>
       <c r="C228" t="n">
         <v>89.12999725341797</v>
@@ -6551,7 +6551,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>77.74269104003906</v>
+        <v>77.74270629882812</v>
       </c>
       <c r="C229" t="n">
         <v>82.31999969482422</v>
@@ -6580,7 +6580,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>79.28205108642578</v>
+        <v>79.28204345703125</v>
       </c>
       <c r="C230" t="n">
         <v>83.94999694824219</v>
@@ -6609,7 +6609,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>85.51679992675781</v>
+        <v>85.51680755615234</v>
       </c>
       <c r="C231" t="n">
         <v>89.79000091552734</v>
@@ -6725,7 +6725,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.19542694091797</v>
+        <v>88.1954345703125</v>
       </c>
       <c r="C235" t="n">
         <v>91.83000183105469</v>
@@ -6783,7 +6783,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>89.34969329833984</v>
+        <v>89.34970092773438</v>
       </c>
       <c r="C237" t="n">
         <v>92.30000305175781</v>
@@ -6841,7 +6841,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>91.03407287597656</v>
+        <v>91.03408050537109</v>
       </c>
       <c r="C239" t="n">
         <v>94.04000091552734</v>
@@ -6870,7 +6870,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>88.93308258056641</v>
+        <v>88.93307495117188</v>
       </c>
       <c r="C240" t="n">
         <v>91.12000274658203</v>
